--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,6 +2095,136 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120540655</v>
+      </c>
+      <c r="B12" t="n">
+        <v>42965</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>526742</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6707981</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 8 exemplar på slingan. Kl. 16:39-17:22. 74% solsekn, SV vind 3-4. 50% moln, + 17 grader.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,139 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125995152</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43218</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Barkargärdet kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>526771</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6707984</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 16 individer längs slingar Barkargärdet. Inventering kl. 14:02-15:03. + 25 grader, molnighet 30%, sydlig vind 3. 90% solsken.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>125995152</v>
       </c>
       <c r="B13" t="n">
-        <v>43218</v>
+        <v>43226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>125995152</v>
       </c>
       <c r="B13" t="n">
-        <v>43226</v>
+        <v>43228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>125995152</v>
       </c>
       <c r="B13" t="n">
-        <v>43228</v>
+        <v>43255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>125995152</v>
       </c>
       <c r="B13" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>125995152</v>
       </c>
       <c r="B13" t="n">
-        <v>43256</v>
+        <v>43258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54041669</v>
+        <v>54041667</v>
       </c>
       <c r="B2" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526752.2724156776</v>
+        <v>526789</v>
       </c>
       <c r="R2" t="n">
-        <v>6707981.542507141</v>
+        <v>6707968</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -818,19 +813,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54041670</v>
+        <v>54041668</v>
       </c>
       <c r="B3" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -853,7 +843,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526722.0971694259</v>
+        <v>526760</v>
       </c>
       <c r="R3" t="n">
-        <v>6707992.156198874</v>
+        <v>6707982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -961,19 +951,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54041668</v>
+        <v>54041669</v>
       </c>
       <c r="B4" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1018,10 +1003,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526760.1662247586</v>
+        <v>526752</v>
       </c>
       <c r="R4" t="n">
-        <v>6707981.600930025</v>
+        <v>6707982</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1104,19 +1089,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61976253</v>
+        <v>54041670</v>
       </c>
       <c r="B5" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1139,7 +1119,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1147,31 +1127,24 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barkargärdet, Dlr</t>
+          <t>Barkargärdet kraftledningsgata, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526772.0871860808</v>
+        <v>526722</v>
       </c>
       <c r="R5" t="n">
-        <v>6707970.852294193</v>
+        <v>6707992</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1198,27 +1171,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2015-06-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2015-06-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning</t>
+          <t>Sammanlagt 20 ex räknades längs en slinga på 1400 meter. Fler exemplar flög i ledningsgatan men kom inte med i linjetaxeringen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,6 +1202,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1238,7 +1216,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Blomkvist</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1249,19 +1227,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61976254</v>
+        <v>61976252</v>
       </c>
       <c r="B6" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1313,10 +1286,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526755.2435301173</v>
+        <v>526798</v>
       </c>
       <c r="R6" t="n">
-        <v>6707980.086737965</v>
+        <v>6707967</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1394,19 +1367,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66271549</v>
+        <v>61976253</v>
       </c>
       <c r="B7" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1458,10 +1426,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526748.3437331079</v>
+        <v>526772</v>
       </c>
       <c r="R7" t="n">
-        <v>6707979.050508908</v>
+        <v>6707971</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1488,22 +1456,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1518,12 +1491,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
+          <t>Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1534,19 +1507,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74345208</v>
+        <v>61976254</v>
       </c>
       <c r="B8" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1582,7 +1550,6 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>friflygande</t>
@@ -1599,13 +1566,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526779.9226392998</v>
+        <v>526755</v>
       </c>
       <c r="R8" t="n">
-        <v>6707978.791710667</v>
+        <v>6707980</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1629,27 +1596,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-06-10</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-06-10</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning. Totalt 9 stycken ex. på denna slingan (Barkargärdet). Betydligt färre fjärilar än andra år. Möjligen för molnigt. Inventering 14:47-15:17. + 26 grader, stilla, kvalmigt, hög luftfuktighet, åskmuller. Sol i början med från 14:53 gick solen i moln. Ytterligare två inventeringar genomfördes här detta år (4:e resp. 20 juni) men alla med dåligt resultat, i jämförelse med andra år.</t>
+          <t>Biogeografisk övervakning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1658,7 +1625,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1670,7 +1636,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1681,19 +1647,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89134196</v>
+        <v>61976256</v>
       </c>
       <c r="B9" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1716,7 +1677,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1729,23 +1690,26 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+          <t>Barkargärdet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526748.7933629162</v>
+        <v>526718</v>
       </c>
       <c r="R9" t="n">
-        <v>6707984.964860296</v>
+        <v>6707993</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1772,27 +1736,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+          <t>Biogeografisk övervakning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1801,7 +1765,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1776,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1824,19 +1787,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95270697</v>
+        <v>61976257</v>
       </c>
       <c r="B10" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1862,29 +1820,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+          <t>Barkargärdet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526740.4207719221</v>
+        <v>526709</v>
       </c>
       <c r="R10" t="n">
-        <v>6707982.932580303</v>
+        <v>6707994</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1911,27 +1876,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning. Molnfritt, plus 26 grader. V vind styrka 2-4. Tid kl. 11.35 till 12.50. Totalt 7 ex på slingan.</t>
+          <t>Biogeografisk övervakning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1940,19 +1905,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Eriksson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Eriksson</t>
+          <t>Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1963,19 +1927,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110231785</v>
+        <v>61976258</v>
       </c>
       <c r="B11" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2001,32 +1960,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Barkargärdet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526745.3434686876</v>
+        <v>526704</v>
       </c>
       <c r="R11" t="n">
-        <v>6707984.446750971</v>
+        <v>6707997</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2050,27 +2016,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning Brun gräsfjäril, Barkargärdet.  Starttid 09.40, sluttid 11,05, temp 18 grader vid start och 21 grader vid slut. molnighet 3/8, vindriktning N vindstyrka 2, sol 80% av tiden. Totalt antal fjärilar på slingan 7 st. Kraftledningen röjd sedan senaste uppföljningen 2022, riset ihopdraget i högar i större delen av området, men i NV delen ligger riset spritt över hela ytan.</t>
+          <t>Biogeografisk övervakning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2079,19 +2045,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristin Persdotter</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristin Persdotter</t>
+          <t>Maria Blomkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2102,19 +2067,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120540655</v>
+        <v>66271549</v>
       </c>
       <c r="B12" t="n">
-        <v>42983</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2155,16 +2115,21 @@
           <t>friflygande</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Barkargärdet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526742</v>
+        <v>526748</v>
       </c>
       <c r="R12" t="n">
-        <v>6707981</v>
+        <v>6707979</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2191,17 +2156,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Biogeografisk övervakning. Totalt 8 exemplar på slingan. Kl. 16:39-17:22. 74% solsekn, SV vind 3-4. 50% moln, + 17 grader.</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2216,12 +2176,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Matilda Elgerud</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2232,14 +2192,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125995152</v>
+        <v>66271551</v>
       </c>
       <c r="B13" t="n">
-        <v>43258</v>
+        <v>43450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2262,7 +2222,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2270,26 +2235,29 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barkargärdet kraftledningsgata, Dlr</t>
+          <t>Barkargärdet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526771</v>
+        <v>526781</v>
       </c>
       <c r="R13" t="n">
-        <v>6707984</v>
+        <v>6707970</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2313,27 +2281,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Biogeografisk övervakning. Totalt 16 individer längs slingar Barkargärdet. Inventering kl. 14:02-15:03. + 25 grader, molnighet 30%, sydlig vind 3. 90% solsken.</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2342,26 +2295,2011 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>71953616</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgatan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>526789</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6707973</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med ”Totalt 8 ex på hela slingan. Biogeografisk övervakning. Inventering 12:30-15:30. +20 grader, klart, vind 4 och 6 i byarna. På grund av hårda vindbyar tog inventeringen lång tid. Stod och inväntade lugnare vind flera gånger och övervägde att avbryta inventeringen. (7-8 ex bruna gräsfjärilar flög utanför inventeringsradien). Med tanke på den hårda vinden så indikerar 8 exemplar BG att många flyger nu, trots att det bara är den 4 juni.”</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74345207</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>526707</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6707990</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-06-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-06-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 9 stycken ex. på denna slingan (Barkargärdet). Betydligt färre fjärilar än andra år. Möjligen för molnigt. Inventering 14:47-15:17. + 26 grader, stilla, kvalmigt, hög luftfuktighet, åskmuller. Sol i början med från 14:53 gick solen i moln. Ytterligare två inventeringar genomfördes här detta år (4:e resp. 20 juni) men alla med dåligt resultat, i jämförelse med andra år.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74345208</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>526780</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6707979</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-06-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-06-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 9 stycken ex. på denna slingan (Barkargärdet). Betydligt färre fjärilar än andra år. Möjligen för molnigt. Inventering 14:47-15:17. + 26 grader, stilla, kvalmigt, hög luftfuktighet, åskmuller. Sol i början med från 14:53 gick solen i moln. Ytterligare två inventeringar genomfördes här detta år (4:e resp. 20 juni) men alla med dåligt resultat, i jämförelse med andra år.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80652764</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>526793</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6707972</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Soligt och varmt, runt 20 grader, stilla. 19 ex på slingan. Skuggigt mot slutet. Brösthög vegetation kring smala stigen i kraftledningsgatan.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>80652795</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>526696</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6708000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Soligt och varmt, runt 20 grader, stilla. 19 ex på slingan. Skuggigt mot slutet. Brösthög vegetation kring smala stigen i kraftledningsgatan.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89134196</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>526749</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6707985</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89134197</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>526778</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6707974</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89134198</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>526782</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6707967</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>89134199</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>526795</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6707965</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>89134200</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>526798</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6707963</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 24 ex på hela slingan. Solsken 100 %. Svag ostlig vind (1-2), Plus 26 grader, Molnighet 1/8 - stackmoln.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>95270697</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Barkargärdet, kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>526740</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6707983</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Molnfritt, plus 26 grader. V vind styrka 2-4. Tid kl. 11.35 till 12.50. Totalt 7 ex på slingan.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>110231785</v>
+      </c>
+      <c r="B25" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>526745</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6707984</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning Brun gräsfjäril, Barkargärdet.  Starttid 09.40, sluttid 11,05, temp 18 grader vid start och 21 grader vid slut. molnighet 3/8, vindriktning N vindstyrka 2, sol 80% av tiden. Totalt antal fjärilar på slingan 7 st. Kraftledningen röjd sedan senaste uppföljningen 2022, riset ihopdraget i högar i större delen av området, men i NV delen ligger riset spritt över hela ytan.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristin Persdotter</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristin Persdotter</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120540655</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>526742</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6707981</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 8 exemplar på slingan. Kl. 16:39-17:22. 74% solsekn, SV vind 3-4. 50% moln, + 17 grader.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125995152</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Barkargärdet kraftledningsgata, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>526771</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6707984</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 16 individer längs slingar Barkargärdet. Inventering kl. 14:02-15:03. + 25 grader, molnighet 30%, sydlig vind 3. 90% solsken.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>66271597</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Barkargärdet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>526781</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6707970</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2017-06-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2017-06-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21302-2022 artfynd.xlsx
+++ b/artfynd/A 21302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -810,6 +815,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54041667</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -948,6 +958,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54041668</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1086,6 +1101,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54041669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1224,6 +1244,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54041670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1364,6 +1389,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1504,6 +1534,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976253</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1644,6 +1679,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1784,6 +1824,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976256</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1924,6 +1969,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976257</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2064,6 +2114,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61976258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2189,6 +2244,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66271549</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2314,6 +2374,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66271551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2437,6 +2502,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71953616</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2569,6 +2639,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74345207</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2701,6 +2776,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74345208</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2843,6 +2923,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80652764</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2985,6 +3070,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80652795</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3123,6 +3213,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89134196</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3261,6 +3356,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89134197</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3399,6 +3499,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89134198</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3537,6 +3642,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89134199</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3675,6 +3785,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89134200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3799,6 +3914,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95270697</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3923,6 +4043,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231785</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4048,6 +4173,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120540655</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4181,6 +4311,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125995152</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4300,8 +4435,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66271597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>